--- a/reports/集团总公司_利润表_2025-07.xlsx
+++ b/reports/集团总公司_利润表_2025-07.xlsx
@@ -2044,7 +2044,7 @@
         </is>
       </c>
       <c r="F3" s="13" t="n">
-        <v>244665712</v>
+        <v>267781789</v>
       </c>
       <c r="G3" s="13" t="n"/>
       <c r="I3" s="5" t="n"/>
@@ -2071,10 +2071,10 @@
         </is>
       </c>
       <c r="F4" s="14" t="n">
-        <v>185926540</v>
+        <v>203154720</v>
       </c>
       <c r="G4" s="14" t="n">
-        <v>1157398331</v>
+        <v>1256165525</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2100,10 +2100,10 @@
         </is>
       </c>
       <c r="F5" s="14" t="n">
-        <v>762992</v>
+        <v>981524</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>4717386</v>
+        <v>6108442</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2128,10 +2128,10 @@
         </is>
       </c>
       <c r="F6" s="14" t="n">
-        <v>664173</v>
+        <v>858789</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>4094966</v>
+        <v>5344181</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2156,10 +2156,10 @@
         </is>
       </c>
       <c r="F7" s="14" t="n">
-        <v>560798</v>
+        <v>725414</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>3468650</v>
+        <v>4510695</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2184,10 +2184,10 @@
         </is>
       </c>
       <c r="F8" s="14" t="n">
-        <v>517938</v>
+        <v>670463</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>3193796</v>
+        <v>4163183</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2212,10 +2212,10 @@
         </is>
       </c>
       <c r="F9" s="14" t="n">
-        <v>279856</v>
+        <v>369409</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>1734634</v>
+        <v>2289525</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2240,10 +2240,10 @@
         </is>
       </c>
       <c r="F10" s="14" t="n">
-        <v>224560</v>
+        <v>291541</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>1388827</v>
+        <v>1803789</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2269,7 +2269,7 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>241655395</v>
+        <v>263884649</v>
       </c>
       <c r="G11" s="13" t="n"/>
     </row>
@@ -2295,7 +2295,7 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>182916223</v>
+        <v>199257580</v>
       </c>
       <c r="G12" s="13" t="n"/>
     </row>
@@ -2321,10 +2321,10 @@
         </is>
       </c>
       <c r="F13" s="14" t="n">
-        <v>94147763</v>
+        <v>104040771</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>586618726</v>
+        <v>641728069</v>
       </c>
     </row>
     <row r="14" ht="20.25" customHeight="1">
@@ -2349,10 +2349,10 @@
         </is>
       </c>
       <c r="F14" s="14" t="n">
-        <v>1727240</v>
+        <v>3088630</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>10757865</v>
+        <v>19086590</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2377,10 +2377,10 @@
         </is>
       </c>
       <c r="F15" s="14" t="n">
-        <v>1565508</v>
+        <v>2245150</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>9718158</v>
+        <v>13882539</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2405,10 +2405,10 @@
         </is>
       </c>
       <c r="F16" s="14" t="n">
-        <v>83585790</v>
+        <v>88499356</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>520105782</v>
+        <v>548490038</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2433,10 +2433,10 @@
         </is>
       </c>
       <c r="F17" s="14" t="n">
-        <v>1799009</v>
+        <v>2235998</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>11110675</v>
+        <v>13885425</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2461,10 +2461,10 @@
         </is>
       </c>
       <c r="F18" s="14" t="n">
-        <v>781569</v>
+        <v>1116522</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>4854354</v>
+        <v>6942203</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -2489,10 +2489,10 @@
         </is>
       </c>
       <c r="F19" s="14" t="n">
-        <v>2814019</v>
+        <v>3343976</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>17360822</v>
+        <v>20825659</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -2517,10 +2517,10 @@
         </is>
       </c>
       <c r="F20" s="14" t="n">
-        <v>1232882</v>
+        <v>1672947</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>7629814</v>
+        <v>10411592</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -2545,10 +2545,10 @@
         </is>
       </c>
       <c r="F21" s="14" t="n">
-        <v>58568714</v>
+        <v>58525663</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>362946530</v>
+        <v>362824780</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -2573,10 +2573,10 @@
         </is>
       </c>
       <c r="F22" s="14" t="n">
-        <v>170458</v>
+        <v>169717</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>1190051</v>
+        <v>1189951</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2601,10 +2601,10 @@
         </is>
       </c>
       <c r="F23" s="14" t="n">
-        <v>0</v>
+        <v>3556523</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>0</v>
+        <v>22063669</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2629,10 +2629,10 @@
         </is>
       </c>
       <c r="F24" s="14" t="n">
-        <v>0</v>
+        <v>2375166</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>0</v>
+        <v>14708088</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>176978756</v>
+        <v>201657219</v>
       </c>
       <c r="G25" s="13" t="n"/>
     </row>
@@ -2683,7 +2683,7 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>142053981</v>
+        <v>150976933</v>
       </c>
       <c r="G26" s="13" t="n"/>
     </row>
@@ -2709,10 +2709,10 @@
         </is>
       </c>
       <c r="F27" s="14" t="n">
-        <v>111597524</v>
+        <v>120569642</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>694877476</v>
+        <v>743731425</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2737,10 +2737,10 @@
         </is>
       </c>
       <c r="F28" s="14" t="n">
-        <v>30456457</v>
+        <v>30407291</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>188193547</v>
+        <v>188136797</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2765,10 +2765,10 @@
         </is>
       </c>
       <c r="F29" s="14" t="n">
-        <v>0</v>
+        <v>5956330</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>0</v>
+        <v>36784899</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2793,10 +2793,10 @@
         </is>
       </c>
       <c r="F30" s="14" t="n">
-        <v>0</v>
+        <v>1903551</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>0</v>
+        <v>11772660</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2821,10 +2821,10 @@
         </is>
       </c>
       <c r="F31" s="14" t="n">
-        <v>0</v>
+        <v>1187730</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>0</v>
+        <v>7358581</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2849,10 +2849,10 @@
         </is>
       </c>
       <c r="F32" s="14" t="n">
-        <v>0</v>
+        <v>1422776</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>0</v>
+        <v>8830635</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -2877,10 +2877,10 @@
         </is>
       </c>
       <c r="F33" s="14" t="n">
-        <v>0</v>
+        <v>1065454</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>0</v>
+        <v>6622843</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -2905,10 +2905,10 @@
         </is>
       </c>
       <c r="F34" s="14" t="n">
-        <v>0</v>
+        <v>709572</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>0</v>
+        <v>4414895</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -2933,10 +2933,10 @@
         </is>
       </c>
       <c r="F35" s="14" t="n">
-        <v>0</v>
+        <v>591104</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>0</v>
+        <v>3678648</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -2961,10 +2961,10 @@
         </is>
       </c>
       <c r="F36" s="14" t="n">
-        <v>3297062</v>
+        <v>3293512</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>20458527</v>
+        <v>20471072</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -2989,10 +2989,10 @@
         </is>
       </c>
       <c r="F37" s="14" t="n">
-        <v>1565748</v>
+        <v>1549741</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>9650897</v>
+        <v>9646192</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -3017,10 +3017,10 @@
         </is>
       </c>
       <c r="F38" s="14" t="n">
-        <v>4024918</v>
+        <v>4040018</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>24973926</v>
+        <v>24975050</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -3045,10 +3045,10 @@
         </is>
       </c>
       <c r="F39" s="14" t="n">
-        <v>26135397</v>
+        <v>26177093</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>161743782</v>
+        <v>161650803</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -3073,10 +3073,10 @@
         </is>
       </c>
       <c r="F40" s="14" t="n">
-        <v>349706</v>
+        <v>3208907</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>2449955</v>
+        <v>19775689</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -3101,10 +3101,10 @@
         </is>
       </c>
       <c r="F41" s="14" t="n">
-        <v>1117692</v>
+        <v>1124239</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>7839505</v>
+        <v>7838099</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3129,10 +3129,10 @@
         </is>
       </c>
       <c r="F42" s="14" t="n">
-        <v>1160816</v>
+        <v>1073305</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>8123466</v>
+        <v>7488575</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -3157,10 +3157,10 @@
         </is>
       </c>
       <c r="F43" s="14" t="n">
-        <v>119394</v>
+        <v>120503</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>839815</v>
+        <v>839845</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3185,10 +3185,10 @@
         </is>
       </c>
       <c r="F44" s="14" t="n">
-        <v>0</v>
+        <v>478566</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>0</v>
+        <v>3338749</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3213,10 +3213,10 @@
         </is>
       </c>
       <c r="F45" s="14" t="n">
-        <v>0</v>
+        <v>1040789</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>0</v>
+        <v>6438269</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3241,10 +3241,10 @@
         </is>
       </c>
       <c r="F46" s="14" t="n">
-        <v>0</v>
+        <v>318067</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>0</v>
+        <v>2226302</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -3269,10 +3269,10 @@
         </is>
       </c>
       <c r="F47" s="14" t="n">
-        <v>0</v>
+        <v>238134</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>0</v>
+        <v>1669854</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -3297,10 +3297,10 @@
         </is>
       </c>
       <c r="F48" s="14" t="n">
-        <v>0</v>
+        <v>396306</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>0</v>
+        <v>2783208</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -3325,10 +3325,10 @@
         </is>
       </c>
       <c r="F49" s="14" t="n">
-        <v>0</v>
+        <v>1478143</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>0</v>
+        <v>9197569</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3353,10 +3353,10 @@
         </is>
       </c>
       <c r="F50" s="14" t="n">
-        <v>0</v>
+        <v>211110</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>0</v>
+        <v>1484302</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
@@ -3381,10 +3381,10 @@
         </is>
       </c>
       <c r="F51" s="14" t="n">
-        <v>0</v>
+        <v>158411</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>0</v>
+        <v>1113130</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -3409,10 +3409,10 @@
         </is>
       </c>
       <c r="F52" s="14" t="n">
-        <v>0</v>
+        <v>264320</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>0</v>
+        <v>1855026</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
@@ -3437,10 +3437,10 @@
         </is>
       </c>
       <c r="F53" s="14" t="n">
-        <v>0</v>
+        <v>185320</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>0</v>
+        <v>1298380</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3465,10 +3465,10 @@
         </is>
       </c>
       <c r="F54" s="14" t="n">
-        <v>0</v>
+        <v>132605</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>0</v>
+        <v>927329</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="F55" s="14" t="n">
-        <v>0</v>
+        <v>106256</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>0</v>
+        <v>741821</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3521,10 +3521,10 @@
         </is>
       </c>
       <c r="F56" s="14" t="n">
-        <v>0</v>
+        <v>79788</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>0</v>
+        <v>556357</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3549,7 +3549,7 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>64676639</v>
+        <v>65752599</v>
       </c>
       <c r="G57" s="13" t="n"/>
     </row>
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>69923409</v>
+        <v>70403086</v>
       </c>
       <c r="G58" s="13" t="n"/>
     </row>
@@ -3601,10 +3601,10 @@
         </is>
       </c>
       <c r="F59" s="14" t="n">
-        <v>0</v>
+        <v>595458</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>0</v>
+        <v>3678623</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3629,10 +3629,10 @@
         </is>
       </c>
       <c r="F60" s="14" t="n">
-        <v>0</v>
+        <v>132726</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>0</v>
+        <v>927543</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="F61" s="14" t="n">
-        <v>209244</v>
+        <v>209996</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>1469512</v>
+        <v>1470215</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3685,7 +3685,7 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>64467395</v>
+        <v>66138061</v>
       </c>
       <c r="G62" s="13" t="n"/>
     </row>
@@ -3711,10 +3711,10 @@
         </is>
       </c>
       <c r="F63" s="14" t="n">
-        <v>7080449</v>
+        <v>7078287</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>49670230</v>
+        <v>49712863</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -3739,7 +3739,7 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>57386946</v>
+        <v>59059774</v>
       </c>
       <c r="G64" s="13" t="n"/>
     </row>
@@ -3789,7 +3789,7 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>57386946</v>
+        <v>59059774</v>
       </c>
       <c r="G66" s="13" t="n"/>
     </row>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>57386946</v>
+        <v>59059774</v>
       </c>
       <c r="G69" s="13" t="n"/>
     </row>
@@ -4041,7 +4041,7 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>57386946</v>
+        <v>59059774</v>
       </c>
       <c r="G76" s="13" t="n"/>
     </row>
@@ -4067,7 +4067,7 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>57386946</v>
+        <v>59059774</v>
       </c>
       <c r="G77" s="13" t="n"/>
     </row>
